--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.41" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.41" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.41.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.41.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0041.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0041.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.41" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.41" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -603,18 +603,18 @@
           <t>L74: suspicious token(s): WILLALL1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "appearance" vs "place county WILLALL1 1 1" :: place county WILLALL1-1:1</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: may order that the Subp Ã¦ na to appear to and</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: to these â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]Affidavi</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]Affidavi</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L27: symbol-only separator/garbage line :: 1850.</t>
@@ -630,7 +630,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Service of copy" vs "3aof CODY" :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Service of copy" vs "3aof CODY" :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -667,15 +667,15 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Service of copy" vs "3aof CODY" :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ ena out of</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr"/>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Service of copy" vs "3aof CODY" :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to these €</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -716,7 +716,7 @@
       <c r="F4" s="1" t="inlineStr"/>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Service of copy" vs "3aof CODY" :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Service of copy" vs "3aof CODY" :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr"/>
@@ -725,11 +725,7 @@
           <t>L89: suspicious token(s): TAbsent (odd internal casing) :: TAbsent</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: place or country within which the Subp Ã¦ na is to be</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
@@ -758,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,11 +768,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served) after service of the Subp Ã¦ na, within which</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -819,11 +811,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: such Defendant was duly served with the Subp Ã¦ na,</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -866,11 +854,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: may order that the Subp Ã¦ na to appear to and</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -913,11 +897,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ ena out of</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -960,11 +940,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: place or country within which the Subp Ã¦ na is to be</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -993,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1007,11 +983,7 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served) after service of the Subp Ã¦ na, within which</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
@@ -1045,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1054,11 +1026,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L144: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: such Defendant was duly served with the Subp Ã¦ na,</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
